--- a/data/trans_camb/P16A05-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P16A05-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 1,09</t>
+          <t>-0,58; 1,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 1,56</t>
+          <t>-0,56; 1,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 0,0</t>
+          <t>-1,14; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,38; -0,02</t>
+          <t>-3,22; 0,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 1,67</t>
+          <t>-2,45; 1,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 0,98</t>
+          <t>-3,23; 1,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 0,15</t>
+          <t>-1,57; 0,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 1,14</t>
+          <t>-1,15; 1,1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 0,22</t>
+          <t>-1,81; 0,29</t>
         </is>
       </c>
     </row>
@@ -798,32 +798,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-92,55; 27,27</t>
+          <t>-91,61; 19,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-72,63; 117,35</t>
+          <t>-73,63; 119,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 137,02</t>
+          <t>-100,0; 200,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-82,63; 27,44</t>
+          <t>-81,52; 31,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-60,22; 140,76</t>
+          <t>-60,74; 122,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 131,35</t>
+          <t>-100,0; 182,99</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 2,23</t>
+          <t>-0,87; 2,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 1,52</t>
+          <t>-1,28; 1,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 2,03</t>
+          <t>-1,94; 1,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 2,6</t>
+          <t>-0,74; 2,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 2,51</t>
+          <t>-0,72; 2,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 2,14</t>
+          <t>-1,42; 2,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 1,93</t>
+          <t>-0,43; 2,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 1,55</t>
+          <t>-0,62; 1,56</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 1,29</t>
+          <t>-1,25; 1,16</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-44,31; 187,46</t>
+          <t>-41,42; 192,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-57,63; 137,6</t>
+          <t>-56,74; 163,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-76,55; 196,65</t>
+          <t>-81,34; 190,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-39,9; 244,08</t>
+          <t>-37,45; 258,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-35,05; 276,47</t>
+          <t>-34,7; 274,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-65,3; 226,0</t>
+          <t>-67,28; 198,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-22,1; 152,58</t>
+          <t>-23,07; 152,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-30,39; 120,73</t>
+          <t>-30,12; 121,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-54,34; 97,91</t>
+          <t>-59,06; 90,23</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 3,43</t>
+          <t>-0,03; 3,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,13; 3,36</t>
+          <t>0,05; 3,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,42; 4,04</t>
+          <t>0,24; 3,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 4,26</t>
+          <t>-0,69; 4,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 3,84</t>
+          <t>-0,61; 3,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 3,16</t>
+          <t>-0,95; 3,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,23; 3,19</t>
+          <t>0,18; 3,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,16; 2,96</t>
+          <t>0,16; 3,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 2,92</t>
+          <t>-0,02; 2,91</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 477,23</t>
+          <t>-22,31; 413,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 538,2</t>
+          <t>-13,73; 425,93</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11,15; 638,36</t>
+          <t>3,64; 490,25</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-11,42; 146,78</t>
+          <t>-15,87; 134,4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-14,94; 139,14</t>
+          <t>-14,18; 130,43</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-20,49; 111,54</t>
+          <t>-21,1; 122,56</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,2; 150,64</t>
+          <t>4,04; 152,83</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,92; 144,27</t>
+          <t>-0,32; 144,26</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 132,66</t>
+          <t>-1,6; 136,67</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 3,48</t>
+          <t>-1,05; 3,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 3,41</t>
+          <t>-1,34; 3,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 4,8</t>
+          <t>-2,02; 4,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 5,21</t>
+          <t>-1,4; 5,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 4,17</t>
+          <t>-2,37; 3,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 4,42</t>
+          <t>-1,83; 4,39</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 3,49</t>
+          <t>-0,4; 3,7</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 2,83</t>
+          <t>-0,88; 2,85</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 3,63</t>
+          <t>-1,12; 3,76</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-30,09; 184,2</t>
+          <t>-28,65; 185,25</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-36,59; 179,26</t>
+          <t>-30,86; 154,69</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-45,75; 202,09</t>
+          <t>-47,36; 208,79</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-16,03; 99,14</t>
+          <t>-16,5; 94,87</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-27,08; 81,34</t>
+          <t>-28,44; 66,29</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-21,46; 79,24</t>
+          <t>-21,97; 82,04</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 87,69</t>
+          <t>-7,77; 90,75</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-19,93; 70,85</t>
+          <t>-15,33; 74,14</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-25,37; 85,55</t>
+          <t>-19,81; 85,53</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 1,8</t>
+          <t>-3,78; 1,57</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 5,03</t>
+          <t>-1,13; 5,17</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 4,28</t>
+          <t>-1,1; 4,49</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 7,08</t>
+          <t>-0,88; 7,09</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,95; 9,75</t>
+          <t>1,56; 9,49</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,92; 7,77</t>
+          <t>1,12; 8,09</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 3,76</t>
+          <t>-1,25; 3,57</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,17; 6,3</t>
+          <t>1,3; 6,34</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,51; 5,02</t>
+          <t>0,69; 5,17</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-61,18; 66,69</t>
+          <t>-64,86; 69,35</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-20,74; 167,92</t>
+          <t>-21,05; 192,26</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-24,54; 165,75</t>
+          <t>-21,04; 168,79</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-11,12; 118,01</t>
+          <t>-9,19; 121,69</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>4,85; 161,87</t>
+          <t>14,82; 163,09</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,24; 141,23</t>
+          <t>10,49; 143,09</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-17,27; 81,52</t>
+          <t>-17,02; 75,99</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>15,25; 133,86</t>
+          <t>18,23; 131,28</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>6,52; 106,22</t>
+          <t>5,77; 106,93</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 4,4</t>
+          <t>-3,17; 4,22</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 2,12</t>
+          <t>-4,48; 2,36</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 3,0</t>
+          <t>-2,94; 3,21</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 4,91</t>
+          <t>-4,49; 4,46</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 6,43</t>
+          <t>-3,39; 6,55</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-9,44; 3,82</t>
+          <t>-9,25; 4,01</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 3,23</t>
+          <t>-2,57; 3,43</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 3,42</t>
+          <t>-2,51; 3,35</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 2,84</t>
+          <t>-5,22; 2,51</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-50,55; 143,99</t>
+          <t>-50,76; 133,12</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-61,83; 73,6</t>
+          <t>-64,14; 73,52</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-45,57; 96,79</t>
+          <t>-41,51; 103,94</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-32,67; 59,25</t>
+          <t>-33,59; 52,52</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-21,34; 71,64</t>
+          <t>-25,66; 77,19</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-68,65; 38,99</t>
+          <t>-67,8; 42,04</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-27,02; 51,42</t>
+          <t>-27,35; 50,86</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-23,34; 54,43</t>
+          <t>-26,27; 48,36</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-52,98; 37,76</t>
+          <t>-54,52; 35,34</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 6,28</t>
+          <t>-3,89; 6,3</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 3,25</t>
+          <t>-5,22; 3,18</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 5,28</t>
+          <t>-3,36; 5,29</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,65; 9,97</t>
+          <t>0,48; 10,63</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 8,91</t>
+          <t>-1,22; 8,81</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,88; 12,2</t>
+          <t>4,1; 12,69</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 7,45</t>
+          <t>0,39; 7,11</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 5,34</t>
+          <t>-1,17; 5,79</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2,61; 8,62</t>
+          <t>2,62; 8,46</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-46,44; 130,15</t>
+          <t>-44,22; 146,29</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-57,28; 72,01</t>
+          <t>-55,75; 73,31</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-34,55; 120,53</t>
+          <t>-36,69; 123,05</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3,89; 180,56</t>
+          <t>2,52; 190,27</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-7,95; 158,85</t>
+          <t>-13,32; 144,68</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>26,84; 208,14</t>
+          <t>31,54; 217,32</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 114,91</t>
+          <t>3,46; 123,59</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-16,88; 87,18</t>
+          <t>-12,89; 100,5</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>26,83; 152,74</t>
+          <t>25,51; 145,42</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 1,67</t>
+          <t>-0,03; 1,64</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,8</t>
+          <t>0,11; 1,79</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,53</t>
+          <t>0,49; 2,45</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,86</t>
+          <t>0,56; 2,99</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,55</t>
+          <t>1,14; 3,52</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,79</t>
+          <t>1,1; 3,89</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,07</t>
+          <t>0,58; 2,11</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,36</t>
+          <t>0,91; 2,4</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>1,17; 2,94</t>
+          <t>1,11; 2,92</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 77,42</t>
+          <t>-2,94; 75,01</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>4,03; 81,07</t>
+          <t>2,09; 82,39</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>13,21; 112,3</t>
+          <t>18,27; 108,79</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>10,35; 58,08</t>
+          <t>10,3; 62,99</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>19,88; 74,19</t>
+          <t>20,46; 74,39</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>19,05; 79,45</t>
+          <t>18,63; 81,67</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>13,69; 56,02</t>
+          <t>13,68; 57,31</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>21,77; 65,12</t>
+          <t>21,25; 67,13</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>28,13; 81,43</t>
+          <t>27,45; 80,19</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A05-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P16A05-Edad-trans_camb.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1,64</t>
+          <t>-1,77</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-1,03</t>
+          <t>-1,06</t>
         </is>
       </c>
     </row>
@@ -677,32 +677,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 1,11</t>
+          <t>-0,57; 1,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 1,51</t>
+          <t>-0,57; 1,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 0,0</t>
+          <t>-1,3; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 0,01</t>
+          <t>-3,13; -0,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 1,89</t>
+          <t>-2,36; 1,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 1,48</t>
+          <t>-3,37; 0,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -712,12 +712,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 1,1</t>
+          <t>-1,16; 1,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 0,29</t>
+          <t>-1,88; 0,19</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-66,91%</t>
+          <t>-72,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-74,29%</t>
+          <t>-77,02%</t>
         </is>
       </c>
     </row>
@@ -798,32 +798,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-91,61; 19,12</t>
+          <t>-91,23; 25,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-73,63; 119,59</t>
+          <t>-73,16; 117,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 200,55</t>
+          <t>-100,0; 125,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-81,52; 31,22</t>
+          <t>-79,56; 26,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-60,74; 122,36</t>
+          <t>-62,28; 126,04</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 182,99</t>
+          <t>-100,0; 103,69</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,34</t>
+          <t>-0,25</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,21</t>
+          <t>0,34</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,05</t>
+          <t>0,05</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 2,32</t>
+          <t>-0,95; 2,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 1,61</t>
+          <t>-1,29; 1,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 1,75</t>
+          <t>-1,55; 1,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 2,51</t>
+          <t>-0,6; 2,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 2,37</t>
+          <t>-0,66; 2,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 2,11</t>
+          <t>-1,09; 2,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 2,01</t>
+          <t>-0,36; 1,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 1,56</t>
+          <t>-0,57; 1,45</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 1,16</t>
+          <t>-1,13; 1,23</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-19,34%</t>
+          <t>-13,97%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-3,03%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-41,42; 192,03</t>
+          <t>-47,07; 185,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-56,74; 163,57</t>
+          <t>-55,34; 134,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-81,34; 190,65</t>
+          <t>-72,14; 149,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-37,45; 258,09</t>
+          <t>-31,91; 280,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-34,7; 274,2</t>
+          <t>-32,71; 263,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-67,28; 198,04</t>
+          <t>-51,67; 228,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-23,07; 152,42</t>
+          <t>-17,35; 135,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-30,12; 121,93</t>
+          <t>-26,94; 108,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-59,06; 90,23</t>
+          <t>-53,87; 95,33</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,02</t>
+          <t>1,62</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,1</t>
+          <t>0,82</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,51</t>
+          <t>1,17</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 3,52</t>
+          <t>0,2; 3,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 3,35</t>
+          <t>0,05; 3,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 3,72</t>
+          <t>0,08; 3,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 4,08</t>
+          <t>-0,37; 3,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 3,86</t>
+          <t>-0,65; 3,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 3,45</t>
+          <t>-1,46; 2,83</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,18; 3,12</t>
+          <t>0,12; 3,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,16; 3,0</t>
+          <t>0,13; 2,96</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 2,91</t>
+          <t>-0,26; 2,36</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>152,56%</t>
+          <t>122,38%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>43,63%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-22,31; 413,83</t>
+          <t>-7,07; 515,42</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-13,73; 425,93</t>
+          <t>-3,79; 494,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,64; 490,25</t>
+          <t>-5,47; 458,77</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-15,87; 134,4</t>
+          <t>-11,22; 133,89</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-14,18; 130,43</t>
+          <t>-16,5; 132,53</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-21,1; 122,56</t>
+          <t>-29,07; 94,24</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,04; 152,83</t>
+          <t>3,15; 142,83</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 144,26</t>
+          <t>2,75; 145,78</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 136,67</t>
+          <t>-7,78; 116,24</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,92</t>
+          <t>3,41</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,38</t>
+          <t>0,96</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,48</t>
+          <t>2,21</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 3,68</t>
+          <t>-1,11; 3,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 3,06</t>
+          <t>-1,08; 3,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 4,77</t>
+          <t>0,65; 6,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 5,14</t>
+          <t>-1,26; 5,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 3,62</t>
+          <t>-2,33; 4,09</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 4,39</t>
+          <t>-1,91; 3,49</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 3,7</t>
+          <t>-0,61; 3,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 2,85</t>
+          <t>-1,08; 2,8</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 3,76</t>
+          <t>0,37; 4,08</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>113,92%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>44,71%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-28,65; 185,25</t>
+          <t>-30,71; 216,05</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-30,86; 154,69</t>
+          <t>-32,38; 191,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-47,36; 208,79</t>
+          <t>6,4; 328,46</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-16,5; 94,87</t>
+          <t>-15,82; 94,99</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-28,44; 66,29</t>
+          <t>-26,48; 77,66</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-21,97; 82,04</t>
+          <t>-21,64; 70,25</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-7,77; 90,75</t>
+          <t>-10,71; 85,39</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-15,33; 74,14</t>
+          <t>-18,33; 68,28</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-19,81; 85,53</t>
+          <t>4,31; 102,43</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1,49</t>
+          <t>1,47</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,62</t>
+          <t>4,51</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2,97</t>
+          <t>2,95</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 1,57</t>
+          <t>-3,49; 1,96</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 5,17</t>
+          <t>-1,08; 5,04</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 4,49</t>
+          <t>-1,3; 3,86</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 7,09</t>
+          <t>-0,84; 7,08</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,56; 9,49</t>
+          <t>1,22; 9,71</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,12; 8,09</t>
+          <t>0,89; 7,72</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 3,57</t>
+          <t>-1,13; 3,4</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,3; 6,34</t>
+          <t>1,35; 6,27</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,69; 5,17</t>
+          <t>0,71; 4,8</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>48,99%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-64,86; 69,35</t>
+          <t>-59,62; 73,11</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-21,05; 192,26</t>
+          <t>-19,53; 181,24</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-21,04; 168,79</t>
+          <t>-22,87; 133,81</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-9,19; 121,69</t>
+          <t>-10,6; 120,3</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>14,82; 163,09</t>
+          <t>11,35; 169,74</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,49; 143,09</t>
+          <t>8,61; 133,01</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-17,02; 75,99</t>
+          <t>-17,42; 71,36</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>18,23; 131,28</t>
+          <t>18,19; 128,72</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>5,77; 106,93</t>
+          <t>8,26; 100,54</t>
         </is>
       </c>
     </row>
@@ -1714,29 +1714,29 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
+          <t>-0,04</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>0,02</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>1,67</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>3,06</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
           <t>0,12</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>0,02</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>1,67</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>-1,93</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>0,12</t>
-        </is>
-      </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
           <t>0,38</t>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-0,67</t>
+          <t>1,45</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 4,22</t>
+          <t>-3,65; 4,18</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 2,36</t>
+          <t>-4,6; 2,06</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 3,21</t>
+          <t>-3,31; 2,71</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 4,46</t>
+          <t>-5,07; 4,38</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 6,55</t>
+          <t>-3,11; 6,28</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-9,25; 4,01</t>
+          <t>-0,9; 6,89</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 3,43</t>
+          <t>-2,78; 3,1</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 3,35</t>
+          <t>-2,58; 3,34</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 2,51</t>
+          <t>-1,15; 4,04</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>-0,75%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-17,77%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-8,17%</t>
+          <t>17,78%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-50,76; 133,12</t>
+          <t>-55,27; 123,68</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-64,14; 73,52</t>
+          <t>-66,09; 68,93</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-41,51; 103,94</t>
+          <t>-47,06; 90,04</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-33,59; 52,52</t>
+          <t>-39,25; 49,89</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-25,66; 77,19</t>
+          <t>-23,96; 77,13</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-67,8; 42,04</t>
+          <t>-6,82; 82,8</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-27,35; 50,86</t>
+          <t>-30,12; 47,45</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-26,27; 48,36</t>
+          <t>-28,07; 47,95</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-54,52; 35,34</t>
+          <t>-11,43; 62,19</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1,22</t>
+          <t>1,13</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,56</t>
+          <t>8,85</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>5,61</t>
+          <t>5,74</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 6,3</t>
+          <t>-3,98; 6,16</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 3,18</t>
+          <t>-5,29; 3,31</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 5,29</t>
+          <t>-3,61; 4,94</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,48; 10,63</t>
+          <t>0,2; 9,96</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 8,81</t>
+          <t>-0,66; 9,37</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,1; 12,69</t>
+          <t>4,23; 12,67</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,39; 7,11</t>
+          <t>0,12; 6,86</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 5,79</t>
+          <t>-1,29; 5,45</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2,62; 8,46</t>
+          <t>2,62; 8,64</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>104,59%</t>
+          <t>108,14%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>74,39%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-44,22; 146,29</t>
+          <t>-43,42; 139,65</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-55,75; 73,31</t>
+          <t>-57,54; 74,21</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-36,69; 123,05</t>
+          <t>-36,25; 107,82</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2,52; 190,27</t>
+          <t>-0,33; 165,73</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-13,32; 144,68</t>
+          <t>-7,84; 156,24</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>31,54; 217,32</t>
+          <t>35,81; 224,81</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,46; 123,59</t>
+          <t>0,48; 111,73</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-12,89; 100,5</t>
+          <t>-14,93; 85,99</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>25,51; 145,42</t>
+          <t>24,73; 144,5</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1,52</t>
+          <t>1,68</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,62</t>
+          <t>3,09</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2,1</t>
+          <t>2,42</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 1,64</t>
+          <t>-0,14; 1,63</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,79</t>
+          <t>0,12; 1,76</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,45</t>
+          <t>0,8; 2,52</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,99</t>
+          <t>0,54; 2,94</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,52</t>
+          <t>1,09; 3,53</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,89</t>
+          <t>1,94; 4,12</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,11</t>
+          <t>0,59; 2,11</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,4</t>
+          <t>0,91; 2,34</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>1,11; 2,92</t>
+          <t>1,74; 3,13</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>57,89%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>60,8%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 75,01</t>
+          <t>-5,31; 72,44</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>2,09; 82,39</t>
+          <t>3,01; 81,56</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>18,27; 108,79</t>
+          <t>25,63; 115,25</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>10,3; 62,99</t>
+          <t>8,32; 60,61</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>20,46; 74,39</t>
+          <t>17,47; 72,34</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>18,63; 81,67</t>
+          <t>32,69; 85,97</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>13,68; 57,31</t>
+          <t>12,89; 56,63</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>21,25; 67,13</t>
+          <t>20,4; 63,43</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>27,45; 80,19</t>
+          <t>40,09; 86,95</t>
         </is>
       </c>
     </row>
